--- a/docs/manual/assets/fixtures/demo-doctolib-2-patients.xlsx
+++ b/docs/manual/assets/fixtures/demo-doctolib-2-patients.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>07.06.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
     </row>
